--- a/output/pdf_financials_xlsx/AIDR.xlsx
+++ b/output/pdf_financials_xlsx/AIDR.xlsx
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>10.079845</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>15.648946</v>
       </c>
     </row>
     <row r="93">
@@ -2732,7 +2732,11 @@
           <t>Reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>10.079845</v>
       </c>

--- a/output/pdf_financials_xlsx/AIDR.xlsx
+++ b/output/pdf_financials_xlsx/AIDR.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.922693</v>
+        <v>6.067705</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.582638</v>
+        <v>14.849657</v>
       </c>
     </row>
     <row r="11">
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.231999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.641779</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.231999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.641779</v>
       </c>
     </row>
     <row r="37">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.279192</v>
+        <v>0.047193</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.870278</v>
+        <v>0.228499</v>
       </c>
     </row>
     <row r="49">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
